--- a/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_28_9.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_28_9.xlsx
@@ -513,661 +513,661 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_28_9_0</t>
+          <t>model_28_9_24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9995199170910614</v>
+        <v>0.9996868016120061</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5113108396914874</v>
+        <v>0.6795215716764346</v>
       </c>
       <c r="D2" t="n">
-        <v>0.999945899176007</v>
+        <v>0.9979525699213723</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9999813103023507</v>
+        <v>0.9987242881943664</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9999555999846341</v>
+        <v>0.9985838831995206</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002849979532477845</v>
+        <v>0.0001859280925790985</v>
       </c>
       <c r="H2" t="n">
-        <v>0.290106995831664</v>
+        <v>0.1902498390001291</v>
       </c>
       <c r="I2" t="n">
-        <v>3.535867710972786e-05</v>
+        <v>0.0003434565738782791</v>
       </c>
       <c r="J2" t="n">
-        <v>2.303756809448828e-06</v>
+        <v>0.0007615236112612253</v>
       </c>
       <c r="K2" t="n">
-        <v>1.883121695958835e-05</v>
+        <v>0.0005524900925697521</v>
       </c>
       <c r="L2" t="n">
-        <v>0.006760512306454189</v>
+        <v>0.004941949156929571</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0168818823964564</v>
+        <v>0.01363554518818732</v>
       </c>
       <c r="N2" t="n">
-        <v>1.000338882053369</v>
+        <v>1.000221081215054</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01760057908038776</v>
+        <v>0.01421603857631822</v>
       </c>
       <c r="P2" t="n">
-        <v>132.3260571186163</v>
+        <v>133.1803011160737</v>
       </c>
       <c r="Q2" t="n">
-        <v>203.0208549609719</v>
+        <v>203.8750989584293</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_28_9_1</t>
+          <t>model_28_9_23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9995628865605783</v>
+        <v>0.9996961704822691</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5105163637201364</v>
+        <v>0.6794885648311704</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9999363811757744</v>
+        <v>0.9980274152413753</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999495067958594</v>
+        <v>0.998771814623337</v>
       </c>
       <c r="F3" t="n">
-        <v>0.999943644950849</v>
+        <v>0.9986363322410406</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0002594894199581187</v>
+        <v>0.0001803663264768417</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2905786310878328</v>
+        <v>0.1902694332892994</v>
       </c>
       <c r="I3" t="n">
-        <v>4.157935679841054e-05</v>
+        <v>0.0003309012649339742</v>
       </c>
       <c r="J3" t="n">
-        <v>6.223967078168773e-06</v>
+        <v>0.0007331531770768084</v>
       </c>
       <c r="K3" t="n">
-        <v>2.390166193828966e-05</v>
+        <v>0.0005320273907680431</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00656303001928789</v>
+        <v>0.004919992960759807</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01610867530115741</v>
+        <v>0.01343005310774465</v>
       </c>
       <c r="N3" t="n">
-        <v>1.000308550663121</v>
+        <v>1.000214467894869</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01679445495828255</v>
+        <v>0.01400179827258386</v>
       </c>
       <c r="P3" t="n">
-        <v>132.5135892541276</v>
+        <v>133.2410412561738</v>
       </c>
       <c r="Q3" t="n">
-        <v>203.2083870964832</v>
+        <v>203.9358390985294</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_28_9_2</t>
+          <t>model_28_9_22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9996004971189568</v>
+        <v>0.9997057267115977</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5097731756509611</v>
+        <v>0.6794535334433844</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9999245088542341</v>
+        <v>0.9981048174711776</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9999024836190363</v>
+        <v>0.9988209067642457</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9999276642971179</v>
+        <v>0.9986905305349872</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0002371621678131151</v>
+        <v>0.0001746933359397625</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2910198196297483</v>
+        <v>0.1902902294343663</v>
       </c>
       <c r="I4" t="n">
-        <v>4.933875033263803e-05</v>
+        <v>0.0003179170341482861</v>
       </c>
       <c r="J4" t="n">
-        <v>1.202020658087364e-05</v>
+        <v>0.0007038481065551536</v>
       </c>
       <c r="K4" t="n">
-        <v>3.067947845675583e-05</v>
+        <v>0.0005108822278623496</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006373260301186101</v>
+        <v>0.004896833219941468</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01540007038338186</v>
+        <v>0.01321716066104072</v>
       </c>
       <c r="N4" t="n">
-        <v>1.000282002033678</v>
+        <v>1.000207722321225</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0160556832621429</v>
+        <v>0.01377984255367563</v>
       </c>
       <c r="P4" t="n">
-        <v>132.6935327968941</v>
+        <v>133.3049569745775</v>
       </c>
       <c r="Q4" t="n">
-        <v>203.3883306392497</v>
+        <v>203.9997548169331</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_28_9_3</t>
+          <t>model_28_9_21</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9996333544315638</v>
+        <v>0.9997154330375259</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5090768687639609</v>
+        <v>0.6794162616238073</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9999106829908194</v>
+        <v>0.9981846236061338</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9998431762113308</v>
+        <v>0.998871480256737</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9999083933819419</v>
+        <v>0.9987463771553144</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002176566476876218</v>
+        <v>0.0001689312415773936</v>
       </c>
       <c r="H5" t="n">
-        <v>0.291433177476763</v>
+        <v>0.190312355596526</v>
       </c>
       <c r="I5" t="n">
-        <v>5.837492028646029e-05</v>
+        <v>0.0003045295480638394</v>
       </c>
       <c r="J5" t="n">
-        <v>1.933064289271634e-05</v>
+        <v>0.0006736587577806533</v>
       </c>
       <c r="K5" t="n">
-        <v>3.885278158958831e-05</v>
+        <v>0.0004890939795880139</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006191120291079408</v>
+        <v>0.004872470333072993</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01475319110184714</v>
+        <v>0.01299735517624234</v>
       </c>
       <c r="N5" t="n">
-        <v>1.000258808636543</v>
+        <v>1.000200870797041</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01538126499036853</v>
+        <v>0.0135506794943293</v>
       </c>
       <c r="P5" t="n">
-        <v>132.8651834948311</v>
+        <v>133.3720375608012</v>
       </c>
       <c r="Q5" t="n">
-        <v>203.5599813371867</v>
+        <v>204.0668354031569</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_28_9_4</t>
+          <t>model_28_9_20</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9996619782645916</v>
+        <v>0.9997252688119986</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5084238561679613</v>
+        <v>0.6793765144542416</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9998952483911077</v>
+        <v>0.998266860427482</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9997740505750643</v>
+        <v>0.9989235616887833</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9998864583559232</v>
+        <v>0.9988038991020888</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0002006643039170951</v>
+        <v>0.000163092300966974</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2918208339624236</v>
+        <v>0.1903359512333685</v>
       </c>
       <c r="I6" t="n">
-        <v>6.846251206873772e-05</v>
+        <v>0.0002907343141255681</v>
       </c>
       <c r="J6" t="n">
-        <v>2.785130803374769e-05</v>
+        <v>0.0006425692593246316</v>
       </c>
       <c r="K6" t="n">
-        <v>4.815600436031263e-05</v>
+        <v>0.0004666521120193359</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006019448376001174</v>
+        <v>0.004846772109720327</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0141656028434054</v>
+        <v>0.01277075960806459</v>
       </c>
       <c r="N6" t="n">
-        <v>1.000238603577935</v>
+        <v>1.000193927897413</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01476866188328954</v>
+        <v>0.01331443728369673</v>
       </c>
       <c r="P6" t="n">
-        <v>133.0277543517848</v>
+        <v>133.4423885076463</v>
       </c>
       <c r="Q6" t="n">
-        <v>203.7225521941404</v>
+        <v>204.137186350002</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_28_9_5</t>
+          <t>model_28_9_19</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9996868482507603</v>
+        <v>0.9997351982065011</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5078106687358883</v>
+        <v>0.6793343095318531</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9998785258186612</v>
+        <v>0.998351454337721</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9996971788737088</v>
+        <v>0.9989770819664315</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9998623998294427</v>
+        <v>0.9988630314608432</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001859004057999357</v>
+        <v>0.0001571977834628216</v>
       </c>
       <c r="H7" t="n">
-        <v>0.29218484851042</v>
+        <v>0.1903610058984561</v>
       </c>
       <c r="I7" t="n">
-        <v>7.939188422861665e-05</v>
+        <v>0.0002765436783207435</v>
       </c>
       <c r="J7" t="n">
-        <v>3.732677996353402e-05</v>
+        <v>0.0006106208561426386</v>
       </c>
       <c r="K7" t="n">
-        <v>5.835985965510904e-05</v>
+        <v>0.0004435819511745105</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005865663718352217</v>
+        <v>0.004819626621726922</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01363452990755221</v>
+        <v>0.01253785402143531</v>
       </c>
       <c r="N7" t="n">
-        <v>1.000221048293581</v>
+        <v>1.000186918913058</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01421498007308456</v>
+        <v>0.01307161642406361</v>
       </c>
       <c r="P7" t="n">
-        <v>133.1805989606912</v>
+        <v>133.5160115563557</v>
       </c>
       <c r="Q7" t="n">
-        <v>203.8753968030468</v>
+        <v>204.2108093987113</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_28_9_6</t>
+          <t>model_28_9_18</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9997083913191935</v>
+        <v>0.9997451788349868</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5072342549077202</v>
+        <v>0.6792892795527932</v>
       </c>
       <c r="D8" t="n">
-        <v>0.999860773070251</v>
+        <v>0.9984383306913905</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9996142863027071</v>
+        <v>0.9990319586928373</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9998366800827715</v>
+        <v>0.9989236921668578</v>
       </c>
       <c r="G8" t="n">
-        <v>0.000173111509765811</v>
+        <v>0.000151272851252961</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2925270326586015</v>
+        <v>0.1903877376392199</v>
       </c>
       <c r="I8" t="n">
-        <v>9.09945485231333e-05</v>
+        <v>0.0002619701624317991</v>
       </c>
       <c r="J8" t="n">
-        <v>4.754440512162734e-05</v>
+        <v>0.0005778627342203041</v>
       </c>
       <c r="K8" t="n">
-        <v>6.926828222477387e-05</v>
+        <v>0.0004199155141475458</v>
       </c>
       <c r="L8" t="n">
-        <v>0.005718852907994342</v>
+        <v>0.004791028008213589</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01315718472036518</v>
+        <v>0.01229930287670651</v>
       </c>
       <c r="N8" t="n">
-        <v>1.000205841421746</v>
+        <v>1.000179873763539</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01371731331303822</v>
+        <v>0.01282290966323476</v>
       </c>
       <c r="P8" t="n">
-        <v>133.3231492119781</v>
+        <v>133.5928507796019</v>
       </c>
       <c r="Q8" t="n">
-        <v>204.0179470543338</v>
+        <v>204.2876486219575</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_28_9_7</t>
+          <t>model_28_9_17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9997269764135981</v>
+        <v>0.999755153645839</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5066919214463858</v>
+        <v>0.6792412494814928</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9998422436573684</v>
+        <v>0.9985272546741084</v>
       </c>
       <c r="E9" t="n">
-        <v>0.999526846249209</v>
+        <v>0.9990880731656631</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9998096942316351</v>
+        <v>0.998985736009213</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001620785948930223</v>
+        <v>0.0001453513726417471</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2928489852288353</v>
+        <v>0.1904162503643349</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001031048174394613</v>
+        <v>0.0002470531565918006</v>
       </c>
       <c r="J9" t="n">
-        <v>5.832256870915512e-05</v>
+        <v>0.000544365751750166</v>
       </c>
       <c r="K9" t="n">
-        <v>8.07136930743082e-05</v>
+        <v>0.0003957094541709833</v>
       </c>
       <c r="L9" t="n">
-        <v>0.005578487794708731</v>
+        <v>0.004760833310192766</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01273100918596096</v>
+        <v>0.01205617570549414</v>
       </c>
       <c r="N9" t="n">
-        <v>1.000192722531578</v>
+        <v>1.000172832720584</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01327299460382943</v>
+        <v>0.01256943206500125</v>
       </c>
       <c r="P9" t="n">
-        <v>133.4548583734405</v>
+        <v>133.6727129746086</v>
       </c>
       <c r="Q9" t="n">
-        <v>204.1496562157961</v>
+        <v>204.3675108169643</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_28_9_8</t>
+          <t>model_28_9_16</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9997429434302886</v>
+        <v>0.9997650775347733</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5061811746886988</v>
+        <v>0.6791901998691651</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9998231441180976</v>
+        <v>0.9986181770004843</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9994360822774451</v>
+        <v>0.9991453922771084</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9997817872007653</v>
+        <v>0.9990491338251779</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0001525998840463214</v>
+        <v>0.0001394601234806429</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2931521865673093</v>
+        <v>0.190446555619441</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0001155877038758364</v>
+        <v>0.000231800928429259</v>
       </c>
       <c r="J10" t="n">
-        <v>6.951044996479458e-05</v>
+        <v>0.0005101496721078982</v>
       </c>
       <c r="K10" t="n">
-        <v>9.254980053230083e-05</v>
+        <v>0.000370975148922091</v>
       </c>
       <c r="L10" t="n">
-        <v>0.005444565308641842</v>
+        <v>0.00472904486683166</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01235313256005623</v>
+        <v>0.01180932358268851</v>
       </c>
       <c r="N10" t="n">
-        <v>1.000181451696267</v>
+        <v>1.000165827622513</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01287903098764748</v>
+        <v>0.01231207093627345</v>
       </c>
       <c r="P10" t="n">
-        <v>133.5753823979359</v>
+        <v>133.755463701504</v>
       </c>
       <c r="Q10" t="n">
-        <v>204.2701802402915</v>
+        <v>204.4502615438597</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_28_9_9</t>
+          <t>model_28_9_15</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9997565885779525</v>
+        <v>0.9997748767326634</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5056997921733584</v>
+        <v>0.6791356770894275</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9998036569506593</v>
+        <v>0.9987108386070069</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9993429782983879</v>
+        <v>0.9992037319833956</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9997532448815113</v>
+        <v>0.9991136866402667</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0001444995349533827</v>
+        <v>0.0001336428963097703</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2934379560230574</v>
+        <v>0.1904789226967546</v>
       </c>
       <c r="I11" t="n">
-        <v>0.000128323932464971</v>
+        <v>0.0002162569358707109</v>
       </c>
       <c r="J11" t="n">
-        <v>8.098676861719955e-05</v>
+        <v>0.0004753243584158605</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0001046553505410853</v>
+        <v>0.0003457902271896616</v>
       </c>
       <c r="L11" t="n">
-        <v>0.005318625546887116</v>
+        <v>0.004695504464571953</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01202079593676653</v>
+        <v>0.01156040208253027</v>
       </c>
       <c r="N11" t="n">
-        <v>1.000171819827328</v>
+        <v>1.000158910541649</v>
       </c>
       <c r="O11" t="n">
-        <v>0.01253254610627269</v>
+        <v>0.01205255233251493</v>
       </c>
       <c r="P11" t="n">
-        <v>133.6844685374653</v>
+        <v>133.840678536468</v>
       </c>
       <c r="Q11" t="n">
-        <v>204.3792663798209</v>
+        <v>204.5354763788236</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_28_9_10</t>
+          <t>model_28_9_14</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9997681849743683</v>
+        <v>0.9997844728258766</v>
       </c>
       <c r="C12" t="n">
-        <v>0.505245671756877</v>
+        <v>0.6790774546957365</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9997839275704213</v>
+        <v>0.9988050386920639</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9992484594753066</v>
+        <v>0.9992629202472106</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9997243086362348</v>
+        <v>0.999179217246131</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0001376154131026864</v>
+        <v>0.0001279462408487813</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2937075415192613</v>
+        <v>0.1905134860247261</v>
       </c>
       <c r="I12" t="n">
-        <v>0.000141218464080557</v>
+        <v>0.0002004548634041392</v>
       </c>
       <c r="J12" t="n">
-        <v>9.263748584019933e-05</v>
+        <v>0.0004399925066562612</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0001169279749603782</v>
+        <v>0.0003202238258251281</v>
       </c>
       <c r="L12" t="n">
-        <v>0.005202687880153982</v>
+        <v>0.004660176247093658</v>
       </c>
       <c r="M12" t="n">
-        <v>0.01173095959854463</v>
+        <v>0.01131133240819937</v>
       </c>
       <c r="N12" t="n">
-        <v>1.00016363413574</v>
+        <v>1.000152136828793</v>
       </c>
       <c r="O12" t="n">
-        <v>0.01223037083508875</v>
+        <v>0.01179287924650246</v>
       </c>
       <c r="P12" t="n">
-        <v>133.7820952498209</v>
+        <v>133.927800751271</v>
       </c>
       <c r="Q12" t="n">
-        <v>204.4768930921765</v>
+        <v>204.6225985936266</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_28_9_11</t>
+          <t>model_28_9_13</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9997779686881957</v>
+        <v>0.9997937876669331</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5048172263093119</v>
+        <v>0.6790152303146437</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9997641021389932</v>
+        <v>0.9989004398623701</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9991532679266354</v>
+        <v>0.9993228213253574</v>
       </c>
       <c r="F13" t="n">
-        <v>0.999695200627686</v>
+        <v>0.9992455538239684</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0001318073779403329</v>
+        <v>0.000122416548817507</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2939618852448155</v>
+        <v>0.1905504251052961</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0001541757718752929</v>
+        <v>0.0001844513087824806</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0001043711255474315</v>
+        <v>0.0004042351473942392</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0001292734487113622</v>
+        <v>0.0002943429789785159</v>
       </c>
       <c r="L13" t="n">
-        <v>0.005092667134174261</v>
+        <v>0.004622811645971371</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0114807394335179</v>
+        <v>0.01106420122817309</v>
       </c>
       <c r="N13" t="n">
-        <v>1.000156727984803</v>
+        <v>1.000145561646871</v>
       </c>
       <c r="O13" t="n">
-        <v>0.01196949827960969</v>
+        <v>0.0115352271805104</v>
       </c>
       <c r="P13" t="n">
-        <v>133.8683379183192</v>
+        <v>134.0161619885354</v>
       </c>
       <c r="Q13" t="n">
-        <v>204.5631357606749</v>
+        <v>204.7109598308911</v>
       </c>
     </row>
     <row r="14">
@@ -1177,712 +1177,712 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.99978615238159</v>
+        <v>0.9998027045516041</v>
       </c>
       <c r="C14" t="n">
-        <v>0.504412505989825</v>
+        <v>0.6789488302904727</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9997442950163928</v>
+        <v>0.9989966668614735</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9990580136331766</v>
+        <v>0.9993831303352915</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9996660973442061</v>
+        <v>0.9993123783822222</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0001269491840242829</v>
+        <v>0.000117123100887378</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2942021447094704</v>
+        <v>0.1905898430279757</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0001671211135690612</v>
+        <v>0.0001683092213082186</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0001161124993943156</v>
+        <v>0.0003682342772653491</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0001416169184361149</v>
+        <v>0.0002682717492867838</v>
       </c>
       <c r="L14" t="n">
-        <v>0.004988181901713312</v>
+        <v>0.004583441655699568</v>
       </c>
       <c r="M14" t="n">
-        <v>0.01126717284966743</v>
+        <v>0.01082234267094597</v>
       </c>
       <c r="N14" t="n">
-        <v>1.000150951260054</v>
+        <v>1.000139267375338</v>
       </c>
       <c r="O14" t="n">
-        <v>0.01174683972414093</v>
+        <v>0.01128307220378589</v>
       </c>
       <c r="P14" t="n">
-        <v>133.9434473547408</v>
+        <v>134.1045700638917</v>
       </c>
       <c r="Q14" t="n">
-        <v>204.6382451970965</v>
+        <v>204.7993679062474</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_28_9_13</t>
+          <t>model_28_9_11</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9997929289405575</v>
+        <v>0.9998111148263837</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5040301636990955</v>
+        <v>0.6788777929795926</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9997246070137572</v>
+        <v>0.9990933915335898</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9989632661391897</v>
+        <v>0.9994436021475631</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9996371600147037</v>
+        <v>0.9993794351188019</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0001229263258891056</v>
+        <v>0.0001121303984732376</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2944291196095745</v>
+        <v>0.1906320138443661</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0001799886020239251</v>
+        <v>0.0001520836491427274</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0001277914033844641</v>
+        <v>0.0003321362238827268</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0001538900027041946</v>
+        <v>0.0002421099365127271</v>
       </c>
       <c r="L15" t="n">
-        <v>0.004888953210872037</v>
+        <v>0.004541835126576213</v>
       </c>
       <c r="M15" t="n">
-        <v>0.01108721452345473</v>
+        <v>0.01058916420088185</v>
       </c>
       <c r="N15" t="n">
-        <v>1.000146167806665</v>
+        <v>1.000133330710788</v>
       </c>
       <c r="O15" t="n">
-        <v>0.01155922019941627</v>
+        <v>0.01103996684350515</v>
       </c>
       <c r="P15" t="n">
-        <v>134.0078507171226</v>
+        <v>134.1916961836517</v>
       </c>
       <c r="Q15" t="n">
-        <v>204.7026485594782</v>
+        <v>204.8864940260073</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_28_9_14</t>
+          <t>model_28_9_10</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9997984688190091</v>
+        <v>0.9998188787136006</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5036686848138292</v>
+        <v>0.6788018428524543</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9997051307021192</v>
+        <v>0.9991900066367739</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9988692994943092</v>
+        <v>0.9995039211586243</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9996085016826348</v>
+        <v>0.9994463514030688</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0001196376147298919</v>
+        <v>0.0001075214196388553</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2946437090909433</v>
+        <v>0.1906771011207102</v>
       </c>
       <c r="I16" t="n">
-        <v>0.000192717735587258</v>
+        <v>0.0001358764571751566</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0001393740572115678</v>
+        <v>0.0002961293836793325</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0001660447568059752</v>
+        <v>0.0002160029204272445</v>
       </c>
       <c r="L16" t="n">
-        <v>0.004794758589352516</v>
+        <v>0.004497941781491088</v>
       </c>
       <c r="M16" t="n">
-        <v>0.01093789809469314</v>
+        <v>0.01036925357192384</v>
       </c>
       <c r="N16" t="n">
-        <v>1.000142257304229</v>
+        <v>1.000127850319811</v>
       </c>
       <c r="O16" t="n">
-        <v>0.01140354706115468</v>
+        <v>0.01081069416379464</v>
       </c>
       <c r="P16" t="n">
-        <v>134.0620865229267</v>
+        <v>134.2756409555805</v>
       </c>
       <c r="Q16" t="n">
-        <v>204.7568843652824</v>
+        <v>204.9704387979361</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_28_9_15</t>
+          <t>model_28_9_9</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9998029187581778</v>
+        <v>0.9998258478488433</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5033267454996706</v>
+        <v>0.6787202890528825</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9996859277137629</v>
+        <v>0.9992859639626951</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9987766344496383</v>
+        <v>0.9995637101348016</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9995802399088166</v>
+        <v>0.9995127205061967</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0001169959386119738</v>
+        <v>0.0001033842399078048</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2948466990388371</v>
+        <v>0.1907255149790766</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0002052682332455704</v>
+        <v>0.0001197796074006778</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0001507962712925597</v>
+        <v>0.0002604389425850969</v>
       </c>
       <c r="K17" t="n">
-        <v>0.000178031320099889</v>
+        <v>0.0001901093840194496</v>
       </c>
       <c r="L17" t="n">
-        <v>0.004705409648230325</v>
+        <v>0.004451653553060159</v>
       </c>
       <c r="M17" t="n">
-        <v>0.01081646608703479</v>
+        <v>0.0101678040848457</v>
       </c>
       <c r="N17" t="n">
-        <v>1.000139116170698</v>
+        <v>1.000122930930228</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0112769454415314</v>
+        <v>0.01060066855499366</v>
       </c>
       <c r="P17" t="n">
-        <v>134.1067426729744</v>
+        <v>134.3541160523869</v>
       </c>
       <c r="Q17" t="n">
-        <v>204.80154051533</v>
+        <v>205.0489138947426</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_28_9_16</t>
+          <t>model_28_9_8</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9998064202312704</v>
+        <v>0.9998318442544356</v>
       </c>
       <c r="C18" t="n">
-        <v>0.503003150056589</v>
+        <v>0.6786329405373821</v>
       </c>
       <c r="D18" t="n">
-        <v>0.999667066666911</v>
+        <v>0.9993806532776881</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9986855500638099</v>
+        <v>0.999622520399885</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9995524721627583</v>
+        <v>0.9995780685669866</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0001149173129284541</v>
+        <v>9.982451451703164e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2950387992724456</v>
+        <v>0.1907773688311371</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0002175952481848068</v>
+        <v>0.0001038954665697629</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0001620236478946154</v>
+        <v>0.0002253327334493722</v>
       </c>
       <c r="K18" t="n">
-        <v>0.000189808353197568</v>
+        <v>0.0001646142016003</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0046205206314314</v>
+        <v>0.004402675116712971</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0107199492969162</v>
+        <v>0.009991221873075967</v>
       </c>
       <c r="N18" t="n">
-        <v>1.000136644542633</v>
+        <v>1.00011869817334</v>
       </c>
       <c r="O18" t="n">
-        <v>0.01117631973184016</v>
+        <v>0.01041656887289332</v>
       </c>
       <c r="P18" t="n">
-        <v>134.1425954124638</v>
+        <v>134.4241935367347</v>
       </c>
       <c r="Q18" t="n">
-        <v>204.8373932548194</v>
+        <v>205.1189913790903</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_28_9_17</t>
+          <t>model_28_9_7</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9998090899927716</v>
+        <v>0.9998366669453789</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5026968283395501</v>
+        <v>0.6785393002871529</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9996485795057293</v>
+        <v>0.999473173273106</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9985962784294382</v>
+        <v>0.9996798422927892</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9995252529459809</v>
+        <v>0.9996418122623412</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0001133324271736718</v>
+        <v>9.696155684365895e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2952206450760891</v>
+        <v>0.1908329577287213</v>
       </c>
       <c r="I19" t="n">
-        <v>0.000229677902655663</v>
+        <v>8.837522928635725e-05</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0001730275784789464</v>
+        <v>0.0001911149934425813</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0002013527405673047</v>
+        <v>0.0001397449534314692</v>
       </c>
       <c r="L19" t="n">
-        <v>0.004539916287990018</v>
+        <v>0.004351030634465093</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0106457703889231</v>
+        <v>0.009846905952818832</v>
       </c>
       <c r="N19" t="n">
-        <v>1.000134760005102</v>
+        <v>1.000115293920909</v>
       </c>
       <c r="O19" t="n">
-        <v>0.01109898287416228</v>
+        <v>0.0102661091251357</v>
       </c>
       <c r="P19" t="n">
-        <v>134.1703704491611</v>
+        <v>134.4823919584326</v>
       </c>
       <c r="Q19" t="n">
-        <v>204.8651682915168</v>
+        <v>205.1771898007882</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_28_9_18</t>
+          <t>model_28_9_6</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9998110356915323</v>
+        <v>0.9998400939957059</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5024067685994189</v>
+        <v>0.6784387996900465</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9996305184078994</v>
+        <v>0.9995626374941993</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9985089797514891</v>
+        <v>0.9997351001733582</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9994986540285211</v>
+        <v>0.9997033187040135</v>
       </c>
       <c r="G20" t="n">
-        <v>0.000112177376339513</v>
+        <v>9.492711172865398e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2953928370677594</v>
+        <v>0.1908926192245634</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0002414820948893666</v>
+        <v>7.336759841186751e-05</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0001837883156270607</v>
+        <v>0.0001581293452924777</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0002126340426445044</v>
+        <v>0.0001157485573420067</v>
       </c>
       <c r="L20" t="n">
-        <v>0.004463311160539369</v>
+        <v>0.004296407620292654</v>
       </c>
       <c r="M20" t="n">
-        <v>0.01059138217323466</v>
+        <v>0.009743054537908221</v>
       </c>
       <c r="N20" t="n">
-        <v>1.000133386570683</v>
+        <v>1.00011287482656</v>
       </c>
       <c r="O20" t="n">
-        <v>0.01104227923953286</v>
+        <v>0.01015783654049028</v>
       </c>
       <c r="P20" t="n">
-        <v>134.1908584442197</v>
+        <v>134.5248024116166</v>
       </c>
       <c r="Q20" t="n">
-        <v>204.8856562865754</v>
+        <v>205.2196002539723</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_28_9_19</t>
+          <t>model_28_9_5</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9998123516420977</v>
+        <v>0.9998418638561967</v>
       </c>
       <c r="C21" t="n">
-        <v>0.502131986014557</v>
+        <v>0.6783309608927208</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9996129241050772</v>
+        <v>0.9996479743371135</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9984238334178822</v>
+        <v>0.999787610943681</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9994727220563817</v>
+        <v>0.9997618372559763</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0001113961712377672</v>
+        <v>9.387644608738552e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>0.295555959880123</v>
+        <v>0.1909566369930494</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0002529812038963586</v>
+        <v>5.905233558610587e-05</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0001942837473631884</v>
+        <v>0.000126783557576408</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0002236324756297735</v>
+        <v>9.291786980267677e-05</v>
       </c>
       <c r="L21" t="n">
-        <v>0.004390547998226281</v>
+        <v>0.004238687675039403</v>
       </c>
       <c r="M21" t="n">
-        <v>0.01055443846150837</v>
+        <v>0.009688985813148119</v>
       </c>
       <c r="N21" t="n">
-        <v>1.000132457664402</v>
+        <v>1.000111625513273</v>
       </c>
       <c r="O21" t="n">
-        <v>0.01100376275751436</v>
+        <v>0.01010146599817945</v>
       </c>
       <c r="P21" t="n">
-        <v>134.2048352011223</v>
+        <v>134.5470620872114</v>
       </c>
       <c r="Q21" t="n">
-        <v>204.8996330434779</v>
+        <v>205.241859929567</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_28_9_20</t>
+          <t>model_28_9_4</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9998131194807018</v>
+        <v>0.9998416814098181</v>
       </c>
       <c r="C22" t="n">
-        <v>0.5018715734053342</v>
+        <v>0.6782149498007348</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9995957979672647</v>
+        <v>0.9997279185406989</v>
       </c>
       <c r="E22" t="n">
-        <v>0.998340970954057</v>
+        <v>0.9998366004418777</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9994474854212847</v>
+        <v>0.9998165020011522</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0001109403490735021</v>
+        <v>9.398475413898409e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2957105520541966</v>
+        <v>0.1910255061886706</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0002641743342842441</v>
+        <v>4.564168847709906e-05</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0002044976614064963</v>
+        <v>9.753975861182644e-05</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0002343359978453702</v>
+        <v>7.159072354446274e-05</v>
       </c>
       <c r="L22" t="n">
-        <v>0.004321404357125617</v>
+        <v>0.004177714079576494</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0105328224647291</v>
+        <v>0.009694573437701325</v>
       </c>
       <c r="N22" t="n">
-        <v>1.000131915660681</v>
+        <v>1.000111754298952</v>
       </c>
       <c r="O22" t="n">
-        <v>0.01098122652300092</v>
+        <v>0.01010729149947786</v>
       </c>
       <c r="P22" t="n">
-        <v>134.21303579367</v>
+        <v>134.5447559577186</v>
       </c>
       <c r="Q22" t="n">
-        <v>204.9078336360256</v>
+        <v>205.2395538000742</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_28_9_21</t>
+          <t>model_28_9_3</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9998134204044513</v>
+        <v>0.9998392307188277</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5016247178947154</v>
+        <v>0.6780900659009594</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9995791794364643</v>
+        <v>0.9998011200532415</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9982605062003259</v>
+        <v>0.9998811867527478</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9994229883143454</v>
+        <v>0.9998663487668327</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0001107617077365445</v>
+        <v>9.54395901751799e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2958570961489027</v>
+        <v>0.1910996426662808</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0002750357079425317</v>
+        <v>3.336212837732374e-05</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0002144160254061619</v>
+        <v>7.092439900104923e-05</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0002447258666743468</v>
+        <v>5.214328518643835e-05</v>
       </c>
       <c r="L23" t="n">
-        <v>0.004255714100150047</v>
+        <v>0.004113157903566354</v>
       </c>
       <c r="M23" t="n">
-        <v>0.01052433882657455</v>
+        <v>0.009769318818381346</v>
       </c>
       <c r="N23" t="n">
-        <v>1.000131703243917</v>
+        <v>1.000113484198474</v>
       </c>
       <c r="O23" t="n">
-        <v>0.01097238171880657</v>
+        <v>0.0101852189457577</v>
       </c>
       <c r="P23" t="n">
-        <v>134.216258882859</v>
+        <v>134.5140341484821</v>
       </c>
       <c r="Q23" t="n">
-        <v>204.9110567252146</v>
+        <v>205.2088319908377</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_28_9_22</t>
+          <t>model_28_9_2</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.999813315266265</v>
+        <v>0.999834122122772</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5013907797364028</v>
+        <v>0.6779556859201772</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9995630757147754</v>
+        <v>0.999865906352177</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9981824363275823</v>
+        <v>0.9999203497151793</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9993992355140728</v>
+        <v>0.9999102376528517</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0001108241223056593</v>
+        <v>9.847227347370844e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2959959719452794</v>
+        <v>0.191179416427786</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0002855606177948517</v>
+        <v>2.249422109252409e-05</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0002240391880876187</v>
+        <v>4.754645388307911e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0002548000554250193</v>
+        <v>3.502028043765912e-05</v>
       </c>
       <c r="L24" t="n">
-        <v>0.004193331383724288</v>
+        <v>0.004044923570097152</v>
       </c>
       <c r="M24" t="n">
-        <v>0.01052730365790117</v>
+        <v>0.00992331968011252</v>
       </c>
       <c r="N24" t="n">
-        <v>1.000131777459107</v>
+        <v>1.000117090266279</v>
       </c>
       <c r="O24" t="n">
-        <v>0.01097547276914081</v>
+        <v>0.0103457759429985</v>
       </c>
       <c r="P24" t="n">
-        <v>134.2151321940133</v>
+        <v>134.4514710739757</v>
       </c>
       <c r="Q24" t="n">
-        <v>204.909930036369</v>
+        <v>205.1462689163313</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_28_9_23</t>
+          <t>model_28_9_1</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9998128658937014</v>
+        <v>0.9998259369974205</v>
       </c>
       <c r="C25" t="n">
-        <v>0.5011688999379906</v>
+        <v>0.6778110220983855</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9995474861767134</v>
+        <v>0.9999204001217054</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9981068314533312</v>
+        <v>0.99995292243001</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9993762378062045</v>
+        <v>0.9999468717547169</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0001110908892712725</v>
+        <v>0.0001033313174613796</v>
       </c>
       <c r="H25" t="n">
-        <v>0.296127689378325</v>
+        <v>0.1912652951215533</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0002957494726391728</v>
+        <v>1.33528865115373e-05</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0002333585065245566</v>
+        <v>2.810249223208479e-05</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0002645539895818647</v>
+        <v>2.072768937181104e-05</v>
       </c>
       <c r="L25" t="n">
-        <v>0.004134003944758379</v>
+        <v>0.003972777923375911</v>
       </c>
       <c r="M25" t="n">
-        <v>0.01053996628416204</v>
+        <v>0.01016520129959951</v>
       </c>
       <c r="N25" t="n">
-        <v>1.000132094663269</v>
+        <v>1.000122868001821</v>
       </c>
       <c r="O25" t="n">
-        <v>0.01098867446961686</v>
+        <v>0.01059795496379104</v>
       </c>
       <c r="P25" t="n">
-        <v>134.2103237388806</v>
+        <v>134.3551401155635</v>
       </c>
       <c r="Q25" t="n">
-        <v>204.9051215812362</v>
+        <v>205.0499379579191</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>model_28_9_24</t>
+          <t>model_28_9_0</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9998121228782312</v>
+        <v>0.9998142044419462</v>
       </c>
       <c r="C26" t="n">
-        <v>0.5009584934244165</v>
+        <v>0.6776549063748496</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9995324148324424</v>
+        <v>0.9999624676745176</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9980337586510155</v>
+        <v>0.9999775886632649</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9993540069487042</v>
+        <v>0.9999747858398985</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0001115319753510167</v>
+        <v>0.0001102962692109027</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2962525957738708</v>
+        <v>0.1913579721588923</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0003055996515525495</v>
+        <v>6.296050866134297e-06</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0002423657130123128</v>
+        <v>1.337822696971905e-05</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0002739826822824312</v>
+        <v>9.837164310056171e-06</v>
       </c>
       <c r="L26" t="n">
-        <v>0.004077571726270656</v>
+        <v>0.003896337938184186</v>
       </c>
       <c r="M26" t="n">
-        <v>0.01056087000919038</v>
+        <v>0.01050220306463852</v>
       </c>
       <c r="N26" t="n">
-        <v>1.000132619144778</v>
+        <v>1.000131149805685</v>
       </c>
       <c r="O26" t="n">
-        <v>0.01101046810949633</v>
+        <v>0.01094930359165758</v>
       </c>
       <c r="P26" t="n">
-        <v>134.2023984674549</v>
+        <v>134.2246809125881</v>
       </c>
       <c r="Q26" t="n">
-        <v>204.8971963098105</v>
+        <v>204.9194787549438</v>
       </c>
     </row>
   </sheetData>
